--- a/data-manipulation-scripts/sheets-cleanup/sheets/TENSOR CORRENTE.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/TENSOR CORRENTE.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -63,6 +63,9 @@
   <si>
     <t xml:space="preserve"> </t>
   </si>
+  <si>
+    <t>KIT TENSOR CORRENTE COMANDO HONDA CG TITAN FAN160</t>
+  </si>
 </sst>
 </file>
 
@@ -105,7 +108,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -122,7 +125,7 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -137,9 +140,6 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -401,7 +401,9 @@
       <c r="C2" s="4">
         <v>1.0</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="5">
+        <v>28.0</v>
+      </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -435,7 +437,9 @@
       <c r="C3" s="4">
         <v>2.0</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="5">
+        <v>28.0</v>
+      </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -469,7 +473,9 @@
       <c r="C4" s="4">
         <v>1.0</v>
       </c>
-      <c r="D4" s="5"/>
+      <c r="D4" s="5">
+        <v>28.0</v>
+      </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
@@ -498,8 +504,12 @@
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
+      <c r="C5" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D5" s="2">
+        <v>28.0</v>
+      </c>
       <c r="E5" s="8"/>
     </row>
     <row r="6">
@@ -512,7 +522,9 @@
       <c r="C6" s="9">
         <v>2.0</v>
       </c>
-      <c r="D6" s="6"/>
+      <c r="D6" s="5">
+        <v>28.0</v>
+      </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
@@ -546,7 +558,9 @@
       <c r="C7" s="9">
         <v>1.0</v>
       </c>
-      <c r="D7" s="6"/>
+      <c r="D7" s="5">
+        <v>25.0</v>
+      </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
@@ -574,13 +588,15 @@
       <c r="A8" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>16</v>
+      <c r="B8" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="C8" s="9">
         <v>1.0</v>
       </c>
-      <c r="D8" s="6"/>
+      <c r="D8" s="5">
+        <v>65.0</v>
+      </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
